--- a/jpcore-r4b/develop/StructureDefinition-jp-specimen-common.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-specimen-common.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-specimen-common.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-specimen-common.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="388">
   <si>
     <t>Property</t>
   </si>
@@ -265,8 +265,8 @@
     <t>患者に対して、または患者のために実行されているか実行されたアクション。これは、手術のような身体的介入、または長期サービス、カウンセリング、催眠療法のような低侵襲性である可能性がある。</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Role[classCode=SPEC]</t>
@@ -291,10 +291,10 @@
     <t>論理ID</t>
   </si>
   <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -310,23 +310,23 @@
     <t>リソースに関するメタデータ</t>
   </si>
   <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
     <t>Specimen.meta.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -361,23 +361,27 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Specimen.meta.versionId</t>
   </si>
   <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+    <t>バージョン固有のidentifier (Baajon koyū no shikibetsu-shi) / Version specific identifier</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有のidentifier。この値は、リソースが作成、更新、または削除された場合に変更されます。 / The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。 / The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
   </si>
   <si>
     <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
   </si>
   <si>
     <t>Specimen.meta.lastUpdated</t>
@@ -387,13 +391,13 @@
 </t>
   </si>
   <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
+    <t>リソースのバージョンが最後に変更されたとき / When the resource version last changed</t>
+  </si>
+  <si>
+    <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。 / When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>この値はリソースが初めて作成される場合を除いて常に設定されています。サーバー/リソースマネージャーがこの値を設定します。クライアントが提供する値は関係ありません。これはHTTP Last-Modifiedに相当し、[read](http://hl7.org/fhir/R4B/http.html#read)のインタラクションで同じ値を持つべきです。 / This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
   </si>
   <si>
     <t>Meta.lastUpdated</t>
@@ -406,13 +410,14 @@
 </t>
   </si>
   <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+    <t>リソースがどこから来たかを特定する / Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。 / A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。 / In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
 This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
   </si>
   <si>
@@ -426,13 +431,13 @@
 </t>
   </si>
   <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+    <t>このリソースが適合を主張するプロファイル / Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>このリソースが準拠すると主張する [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) リソースに関するプロファイルのリストです。URL は [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url) への参照です。 / A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>これらの主張が時間の経過に伴って検証または更新される方法と、それらを決定するサーバーや他の基盤に任されます。プロファイルURLのリストは1セットです。 / It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
     <t>Meta.profile</t>
@@ -445,13 +450,13 @@
 </t>
   </si>
   <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+    <t>このリソースに適用されたセキュリティラベル / Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>このリソースにはセキュリティラベルが適用されています。これらのタグにより、特定のリソースが全体的なセキュリティポリシーやインフラストラクチャに関連付けられます。 / Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>セキュリティラベルは変更せずにリソースのバージョンを更新可能です。セキュリティラベルのリストはセットであり、一意性はシステム/コードに基づき、バージョンと表示は無視されます。 / The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -466,13 +471,13 @@
     <t>Specimen.meta.tag</t>
   </si>
   <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+    <t>このリソースに適用されたタグ / Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>このリソースに適用されるタグです。タグは、リソースをプロセスやワークフローに識別し、関連付けるために使用することが意図されており、アプリケーションはリソースの意味を解釈する際にタグを考慮する必要はありません。 / Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>リソースの表示バージョンを変更することなく、タグを更新できます。タグのリストは集合です。ユニーク性はシステム/コードに基づき、バージョンと表示は無視されます。 / The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
   </si>
   <si>
     <t>example</t>
@@ -490,10 +495,10 @@
     <t>このコンテンツが作成されたセット</t>
   </si>
   <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -509,10 +514,10 @@
     <t>リソースコンテンツの言語</t>
   </si>
   <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
@@ -541,10 +546,10 @@
     <t>このリソースを人間が解釈するためのテキスト要約</t>
   </si>
   <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -567,16 +572,16 @@
     <t>インラインリソース含む</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -590,6 +595,10 @@
   </si>
   <si>
     <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Specimen.modifierExtension</t>
@@ -611,7 +620,7 @@
     <t>外部識別子</t>
   </si>
   <si>
-    <t>Id for specimen.</t>
+    <t>標本のID。 / Id for specimen.</t>
   </si>
   <si>
     <t>.id</t>
@@ -629,7 +638,7 @@
     <t>検査部門で採番された識別子</t>
   </si>
   <si>
-    <t>The identifier assigned by the lab when accessioning specimen(s). This is not necessarily the same as the specimen identifier, depending on local lab procedures.</t>
+    <t>試験片を加速するときにラボによって割り当てられたidentifier。これは、ローカルラボのプロシジャー（処置等）に応じて、必ずしも試料identifierと同じではありません。 / The identifier assigned by the lab when accessioning specimen(s). This is not necessarily the same as the specimen identifier, depending on local lab procedures.</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].act[classCode=ACSN, moodCode=EVN].id</t>
@@ -641,13 +650,13 @@
     <t>Specimen.status</t>
   </si>
   <si>
-    <t>available | unavailable | unsatisfactory | entered-in-error</t>
-  </si>
-  <si>
-    <t>The availability of the specimen.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+    <t>利用可能|利用できない|不十分な|エラー入力 / available | unavailable | unsatisfactory | entered-in-error</t>
+  </si>
+  <si>
+    <t>標本の可用性。 / The availability of the specimen.</t>
+  </si>
+  <si>
+    <t>この要素は、リソースを現在有効ではないとマークするコードが含まれているため、修飾子としてラベル付けされています。 / This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
     <t>required</t>
@@ -678,10 +687,10 @@
     <t>検査材料の種類</t>
   </si>
   <si>
-    <t>The kind of material that forms the specimen.</t>
-  </si>
-  <si>
-    <t>The type can change the way that a specimen is handled and drives what kind of analyses can properly be performed on the specimen. It is frequently used in diagnostic work flow decision making systems.</t>
+    <t>標本を形成する種類の材料。 / The kind of material that forms the specimen.</t>
+  </si>
+  <si>
+    <t>このタイプは、標本の処理方法を変更し、どのような分析を試験片で適切に実行できるかを駆動できます。診断作業フローの意思決定システムで頻繁に使用されます。 / The type can change the way that a specimen is handled and drives what kind of analyses can properly be performed on the specimen. It is frequently used in diagnostic work flow decision making systems.</t>
   </si>
   <si>
     <t>標本のタイプ</t>
@@ -709,10 +718,10 @@
     <t>検体の由来（患者からの、環境試験であれば場所、物質や装置から、等）</t>
   </si>
   <si>
-    <t>Where the specimen came from. This may be from patient(s), from a location (e.g., the source of an environmental sample), or a sampling of a substance or a device.</t>
-  </si>
-  <si>
-    <t>Must know the subject context.</t>
+    <t>標本はどこから来たのか。これは、患者、場所（環境サンプルのソースなど）、または物質またはデバイスのサンプリングからのものです。 / Where the specimen came from. This may be from patient(s), from a location (e.g., the source of an environmental sample), or a sampling of a substance or a device.</t>
+  </si>
+  <si>
+    <t>主題のコンテキストを知っている必要があります。 / Must know the subject context.</t>
   </si>
   <si>
     <t>.scoper  or  .scoper.playsRole</t>
@@ -731,7 +740,7 @@
     <t>検体を受領した。または処理を開始した日時</t>
   </si>
   <si>
-    <t>Time when specimen was received for processing or testing.</t>
+    <t>処理またはテストのために標本を受け取った時間。 / Time when specimen was received for processing or testing.</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].act[code=SPCREC, moodCode=EVN].effectiveTime</t>
@@ -753,10 +762,10 @@
     <t>親検体</t>
   </si>
   <si>
-    <t>Reference to the parent (source) specimen which is used when the specimen was either derived from or a component of another specimen.</t>
-  </si>
-  <si>
-    <t>The parent specimen could be the source from which the current specimen is derived by some processing step (e.g. an aliquot or isolate or extracted nucleic acids from clinical samples) or one of many specimens that were combined to create a pooled sample.</t>
+    <t>標本が別の標本の成分から由来するときに使用されるときに使用される親（ソース）標本への参照。 / Reference to the parent (source) specimen which is used when the specimen was either derived from or a component of another specimen.</t>
+  </si>
+  <si>
+    <t>親標本は、現在の標本が何らかの処理ステップ（例えば、臨床サンプルからアリコートまたは分離または抽出された核酸）またはプールされたサンプルを作成する多くの標本の1つによって導出される源である可能性があります。 / The parent specimen could be the source from which the current specimen is derived by some processing step (e.g. an aliquot or isolate or extracted nucleic acids from clinical samples) or one of many specimens that were combined to create a pooled sample.</t>
   </si>
   <si>
     <t>.scoper (if parent) .player.scopesRole[classCode=SPEC].player (if child)</t>
@@ -772,10 +781,10 @@
     <t>検体を採取した理由</t>
   </si>
   <si>
-    <t>Details concerning a service request that required a specimen to be collected.</t>
-  </si>
-  <si>
-    <t>The request may be explicit or implied such with a ServiceRequest that requires a blood draw.</t>
+    <t>標本を収集する必要があるサービス要求に関する詳細。 / Details concerning a service request that required a specimen to be collected.</t>
+  </si>
+  <si>
+    <t>リクエストは、血液の引き分けを必要とするサービスを備えて、明示的または暗示される場合があります。 / The request may be explicit or implied such with a ServiceRequest that requires a blood draw.</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=FLFS].target</t>
@@ -797,10 +806,10 @@
     <t>採取の詳細</t>
   </si>
   <si>
-    <t>Details concerning the specimen collection.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>標本コレクションに関する詳細。 / Details concerning the specimen collection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -817,6 +826,9 @@
 </t>
   </si>
   <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
     <t>Specimen.collection.extension</t>
   </si>
   <si>
@@ -839,7 +851,7 @@
     <t>検体採取者</t>
   </si>
   <si>
-    <t>Person who collected the specimen.</t>
+    <t>標本を集めた人。 / Person who collected the specimen.</t>
   </si>
   <si>
     <t>.participation[typeCode=PFM].role</t>
@@ -861,7 +873,7 @@
     <t>検体採取日時（日時あるいは期間のどちらか）</t>
   </si>
   <si>
-    <t>Time when specimen was collected from subject - the physiologically relevant time.</t>
+    <t>標本が被験者から収集された時間 - 生理学的に関連する時間。 / Time when specimen was collected from subject - the physiologically relevant time.</t>
   </si>
   <si>
     <t>.effectiveTime</t>
@@ -883,7 +895,7 @@
     <t>検体採取に要した期間</t>
   </si>
   <si>
-    <t>The span of time over which the collection of a specimen occurred.</t>
+    <t>標本の収集が発生した時間の範囲。 / The span of time over which the collection of a specimen occurred.</t>
   </si>
   <si>
     <t>Specimen.collection.quantity</t>
@@ -896,7 +908,7 @@
     <t>検体採取量</t>
   </si>
   <si>
-    <t>The quantity of specimen collected; for instance the volume of a blood sample, or the physical measurement of an anatomic pathology sample.</t>
+    <t>収集された標本の量;たとえば、血液サンプルの量、または解剖学的病理サンプルの物理的測定。 / The quantity of specimen collected; for instance the volume of a blood sample, or the physical measurement of an anatomic pathology sample.</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].role[classCode=SPEC].player.quantity</t>
@@ -911,7 +923,7 @@
     <t>検体採取方法</t>
   </si>
   <si>
-    <t>A coded value specifying the technique that is used to perform the procedure.</t>
+    <t>プロシジャー（処置等）の実行に使用される手法を指定するコード化された値。 / A coded value specifying the technique that is used to perform the procedure.</t>
   </si>
   <si>
     <t>採取方法</t>
@@ -932,10 +944,10 @@
     <t>採取部位</t>
   </si>
   <si>
-    <t>Anatomical location from which the specimen was collected (if subject is a patient). This is the target site.  This element is not used for environmental specimens.</t>
-  </si>
-  <si>
-    <t>If the use case requires  BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
+    <t>標本が収集された解剖学的位置（被験者が患者の場合）。これがターゲットサイトです。この要素は、環境標本には使用されません。 / Anatomical location from which the specimen was collected (if subject is a patient). This is the target site.  This element is not used for environmental specimens.</t>
+  </si>
+  <si>
+    <t>ユースケースでは、ボディサイトをインラインコード化された要素の代わりに個別のリソースとして処理する必要がある場合（たとえば、個別に識別および追跡するため）、標準の拡張[BodySite]（Extension-BodySite.html）を使用します。 / If the use case requires  BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -957,13 +969,13 @@
     <t>患者が飲食を控えたかどうか、あるいはどれくらいの期間飲食を控えたか。のどちらか</t>
   </si>
   <si>
-    <t>Abstinence or reduction from some or all food, drink, or both, for a period of time prior to sample collection.</t>
-  </si>
-  <si>
-    <t>Representing fasting status using this element is preferred to representing it with an observation using a 'pre-coordinated code'  such as  LOINC 2005-7 (Calcium [Moles/​time] in 2 hour Urine --12 hours fasting), or  using  a component observation ` such as `Observation.component code`  = LOINC 49541-6 (Fasting status - Reported).</t>
-  </si>
-  <si>
-    <t>Many diagnostic tests require fasting  to facilitate accurate interpretation.</t>
+    <t>サンプル収集の前に、一部またはすべての食べ物、飲み物、またはその両方からの禁欲または削減。 / Abstinence or reduction from some or all food, drink, or both, for a period of time prior to sample collection.</t>
+  </si>
+  <si>
+    <t>この要素を使用して絶食ステータスを表すことは、2時間の尿-12時間の断食でのLOINC 2005-7（カルシウム[モル/時間]）などの「事前調整コード」を使用して観察することでそれを表現することを好むか、またはコンポーネントの観測 `などの` observation.component code` = loinc 49541-6（空腹時ステータス - 報告）。 / Representing fasting status using this element is preferred to representing it with an observation using a 'pre-coordinated code'  such as  LOINC 2005-7 (Calcium [Moles/​time] in 2 hour Urine --12 hours fasting), or  using  a component observation ` such as `Observation.component code`  = LOINC 49541-6 (Fasting status - Reported).</t>
+  </si>
+  <si>
+    <t>多くの診断テストでは、正確な解釈を容易にするために断食が必要です。 / Many diagnostic tests require fasting  to facilitate accurate interpretation.</t>
   </si>
   <si>
     <t>患者の絶食状況</t>
@@ -981,7 +993,7 @@
     <t>検体の処理と詳細</t>
   </si>
   <si>
-    <t>Details concerning processing and processing steps for the specimen.</t>
+    <t>標本の処理と処理に関する詳細。 / Details concerning processing and processing steps for the specimen.</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].act[code=SPCTRT, moodCode=EVN]</t>
@@ -1002,7 +1014,7 @@
     <t>手順のテキストによる説明</t>
   </si>
   <si>
-    <t>Textual description of procedure.</t>
+    <t>プロシジャー（処置等）のテキスト説明。 / Textual description of procedure.</t>
   </si>
   <si>
     <t>.text</t>
@@ -1014,7 +1026,7 @@
     <t>検体に適用される処理</t>
   </si>
   <si>
-    <t>A coded value specifying the procedure used to process the specimen.</t>
+    <t>試料の処理に使用されるプロシジャー（処置等）を指定するコード化された値。 / A coded value specifying the procedure used to process the specimen.</t>
   </si>
   <si>
     <t>材料に対する処理</t>
@@ -1033,7 +1045,7 @@
     <t>処理に使用される材料</t>
   </si>
   <si>
-    <t>Material used in the processing step.</t>
+    <t>処理ステップで使用される材料。 / Material used in the processing step.</t>
   </si>
   <si>
     <t>.participation[typeCode=CSM].role[classCode=ADTV].code</t>
@@ -1048,7 +1060,7 @@
     <t>検体を処理した日時あるいは期間のうちどちらか</t>
   </si>
   <si>
-    <t>A record of the time or period when the specimen processing occurred.  For example the time of sample fixation or the period of time the sample was in formalin.</t>
+    <t>標本処理が発生した時間または期間の記録。たとえば、サンプル固定の時間またはサンプルがホルマリンにあった期間。 / A record of the time or period when the specimen processing occurred.  For example the time of sample fixation or the period of time the sample was in formalin.</t>
   </si>
   <si>
     <t>Specimen.container</t>
@@ -1057,7 +1069,7 @@
     <t>採取容器(採取管/スライドなど)</t>
   </si>
   <si>
-    <t>The container holding the specimen.  The recursive nature of containers; i.e. blood in tube in tray in rack is not addressed here.</t>
+    <t>標本を保持している容器。コンテナの再帰的性質。つまり、ラックのトレイのチューブ内の血液はここでは対処されていません。 / The container holding the specimen.  The recursive nature of containers; i.e. blood in tube in tray in rack is not addressed here.</t>
   </si>
   <si>
     <t>.player.scopingRole[classCode=CONT].scoper</t>
@@ -1078,7 +1090,7 @@
     <t>採取容器のID</t>
   </si>
   <si>
-    <t>Id for container. There may be multiple; a manufacturer's bar code, lab assigned identifier, etc. The container ID may differ from the specimen id in some circumstances.</t>
+    <t>コンテナ用のID。複数があるかもしれません。メーカーのバーコード、ラボに割り当てられたidentifierなど。コンテナIDは、状況によっては試料IDとは異なる場合があります。 / Id for container. There may be multiple; a manufacturer's bar code, lab assigned identifier, etc. The container ID may differ from the specimen id in some circumstances.</t>
   </si>
   <si>
     <t>SAC-3</t>
@@ -1090,7 +1102,7 @@
     <t>採取容器のテキストによる説明</t>
   </si>
   <si>
-    <t>Textual description of the container.</t>
+    <t>コンテナのテキスト説明。 / Textual description of the container.</t>
   </si>
   <si>
     <t>.desc</t>
@@ -1102,7 +1114,7 @@
     <t>検体に直接関係する採取容器の種類</t>
   </si>
   <si>
-    <t>The type of container associated with the specimen (e.g. slide, aliquot, etc.).</t>
+    <t>標本に関連付けられた容器の種類（例：スライド、アリコートなど）。 / The type of container associated with the specimen (e.g. slide, aliquot, etc.).</t>
   </si>
   <si>
     <t>容器種別</t>
@@ -1120,7 +1132,7 @@
     <t>採取容器の容量あるいはサイズ</t>
   </si>
   <si>
-    <t>The capacity (volume or other measure) the container may contain.</t>
+    <t>容量（ボリュームまたはその他の測定）が含まれている場合があります。 / The capacity (volume or other measure) the container may contain.</t>
   </si>
   <si>
     <t>.quantity</t>
@@ -1132,7 +1144,7 @@
     <t>Specimen.container.specimenQuantity</t>
   </si>
   <si>
-    <t>The quantity of specimen in the container; may be volume, dimensions, or other appropriate measurements, depending on the specimen type.</t>
+    <t>容器内の標本の量。試験片の種類に応じて、体積、寸法、またはその他の適切な測定値である場合があります。 / The quantity of specimen in the container; may be volume, dimensions, or other appropriate measurements, depending on the specimen type.</t>
   </si>
   <si>
     <t>.playedRole[classCode=CONT].quantity</t>
@@ -1151,7 +1163,7 @@
     <t>採取容器の添加物（ CodeableConcept または Reference(Substance) のどちらか）</t>
   </si>
   <si>
-    <t>Introduced substance to preserve, maintain or enhance the specimen. Examples: Formalin, Citrate, EDTA.</t>
+    <t>標本を保存、維持、または強化するために物質を導入しました。例：ホルマリン、クエン酸塩、EDTA。 / Introduced substance to preserve, maintain or enhance the specimen. Examples: Formalin, Citrate, EDTA.</t>
   </si>
   <si>
     <t>採取容器の添加物</t>
@@ -1172,13 +1184,13 @@
     <t>検体の状態</t>
   </si>
   <si>
-    <t>A mode or state of being that describes the nature of the specimen.</t>
-  </si>
-  <si>
-    <t>Specimen condition is an observation made about the specimen.  It's a point-in-time assessment.  It can be used to assess its quality or appropriateness for a specific test.</t>
-  </si>
-  <si>
-    <t>The specimen condition can be used to assess its quality or appropriateness for a specific test.</t>
+    <t>標本の性質を説明するモードまたは存在の状態。 / A mode or state of being that describes the nature of the specimen.</t>
+  </si>
+  <si>
+    <t>標本の状態は、標本について行われた観察です。それはポイントインタイム評価です。特定のテストの品質または適切性を評価するために使用できます。 / Specimen condition is an observation made about the specimen.  It's a point-in-time assessment.  It can be used to assess its quality or appropriateness for a specific test.</t>
+  </si>
+  <si>
+    <t>標本の状態を使用して、特定のテストの品質または適切性を評価できます。 / The specimen condition can be used to assess its quality or appropriateness for a specific test.</t>
   </si>
   <si>
     <t>材料の状態を説明するコード</t>
@@ -1200,7 +1212,7 @@
     <t>コメント</t>
   </si>
   <si>
-    <t>To communicate any details or issues about the specimen or during the specimen collection. (for example: broken vial, sent with patient, frozen).</t>
+    <t>標本または標本収集中に詳細または問題を伝える。（例：壊れたバイアル、患者と一緒に送られ、冷凍）。 / To communicate any details or issues about the specimen or during the specimen collection. (for example: broken vial, sent with patient, frozen).</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="annotation"].value</t>
@@ -1540,7 +1552,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="75.7421875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="109.33984375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -2331,7 +2343,7 @@
         <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>76</v>
@@ -2345,10 +2357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2371,16 +2383,16 @@
         <v>87</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2430,7 +2442,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2442,7 +2454,7 @@
         <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>76</v>
@@ -2456,10 +2468,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2482,16 +2494,16 @@
         <v>87</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2541,7 +2553,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2553,7 +2565,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -2567,10 +2579,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2593,16 +2605,16 @@
         <v>87</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2652,7 +2664,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2664,7 +2676,7 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2678,10 +2690,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2704,16 +2716,16 @@
         <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2739,11 +2751,11 @@
         <v>76</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Y11" s="2"/>
       <c r="Z11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>76</v>
@@ -2761,7 +2773,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2773,7 +2785,7 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>76</v>
@@ -2787,10 +2799,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2813,16 +2825,16 @@
         <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2848,11 +2860,11 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>76</v>
@@ -2870,7 +2882,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2882,7 +2894,7 @@
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>76</v>
@@ -2896,10 +2908,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2922,16 +2934,16 @@
         <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2981,7 +2993,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3007,10 +3019,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3033,16 +3045,16 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3068,13 +3080,13 @@
         <v>76</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>76</v>
@@ -3092,7 +3104,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3118,14 +3130,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3144,16 +3156,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3203,7 +3215,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3218,7 +3230,7 @@
         <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>76</v>
@@ -3229,14 +3241,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3255,16 +3267,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3314,7 +3326,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3326,10 +3338,10 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3340,10 +3352,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3369,7 +3381,7 @@
         <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>107</v>
@@ -3423,7 +3435,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3435,7 +3447,7 @@
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>76</v>
@@ -3449,10 +3461,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3478,7 +3490,7 @@
         <v>105</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M18" t="s" s="2">
         <v>107</v>
@@ -3532,7 +3544,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3544,7 +3556,7 @@
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>76</v>
@@ -3558,10 +3570,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3584,13 +3596,13 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3641,7 +3653,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3656,21 +3668,21 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3693,13 +3705,13 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3750,7 +3762,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3765,21 +3777,21 @@
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3802,16 +3814,16 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3837,13 +3849,13 @@
         <v>76</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>76</v>
@@ -3861,7 +3873,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3876,21 +3888,21 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3913,16 +3925,16 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3948,13 +3960,13 @@
         <v>76</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>76</v>
@@ -3972,7 +3984,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3987,21 +3999,21 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4024,17 +4036,17 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -4083,7 +4095,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4098,10 +4110,10 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -4109,10 +4121,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4135,13 +4147,13 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4192,7 +4204,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4207,21 +4219,21 @@
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4244,16 +4256,16 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4303,7 +4315,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4318,7 +4330,7 @@
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
@@ -4329,10 +4341,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4355,16 +4367,16 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4414,7 +4426,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4429,21 +4441,21 @@
         <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4466,13 +4478,13 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4523,7 +4535,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4535,24 +4547,24 @@
         <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4575,13 +4587,13 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>89</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>101</v>
+        <v>259</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4658,10 +4670,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4753,7 +4765,7 @@
         <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>76</v>
@@ -4767,10 +4779,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4796,7 +4808,7 @@
         <v>105</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M30" t="s" s="2">
         <v>107</v>
@@ -4850,7 +4862,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4862,7 +4874,7 @@
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>76</v>
@@ -4876,10 +4888,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4902,13 +4914,13 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4959,7 +4971,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4974,21 +4986,21 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5011,13 +5023,13 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5068,7 +5080,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5083,21 +5095,21 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5120,13 +5132,13 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5177,7 +5189,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5195,7 +5207,7 @@
         <v>76</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5203,10 +5215,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5229,13 +5241,13 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5286,7 +5298,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5301,21 +5313,21 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5338,13 +5350,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5371,31 +5383,31 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5410,21 +5422,21 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5447,16 +5459,16 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5482,13 +5494,13 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -5506,7 +5518,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5521,21 +5533,21 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5558,19 +5570,19 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5595,13 +5607,13 @@
         <v>76</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>76</v>
@@ -5619,7 +5631,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5640,15 +5652,15 @@
         <v>76</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5671,13 +5683,13 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5728,7 +5740,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5740,10 +5752,10 @@
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -5754,10 +5766,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5780,13 +5792,13 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>89</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>101</v>
+        <v>259</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5863,10 +5875,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5958,7 +5970,7 @@
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>76</v>
@@ -5972,10 +5984,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6001,7 +6013,7 @@
         <v>105</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>107</v>
@@ -6055,7 +6067,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6067,7 +6079,7 @@
         <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>76</v>
@@ -6081,10 +6093,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6107,13 +6119,13 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6164,7 +6176,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6179,7 +6191,7 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
@@ -6190,10 +6202,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6216,13 +6228,13 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6249,31 +6261,31 @@
         <v>76</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6288,7 +6300,7 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
@@ -6299,10 +6311,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6325,13 +6337,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6382,7 +6394,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6397,21 +6409,21 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6434,13 +6446,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6491,7 +6503,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6506,7 +6518,7 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>76</v>
@@ -6517,10 +6529,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6543,13 +6555,13 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6600,7 +6612,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6612,10 +6624,10 @@
         <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
@@ -6626,10 +6638,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6652,13 +6664,13 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>89</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>101</v>
+        <v>259</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6735,10 +6747,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6830,7 +6842,7 @@
         <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>76</v>
@@ -6844,10 +6856,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6873,7 +6885,7 @@
         <v>105</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M49" t="s" s="2">
         <v>107</v>
@@ -6927,7 +6939,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6939,7 +6951,7 @@
         <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>76</v>
@@ -6953,10 +6965,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6979,13 +6991,13 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7036,7 +7048,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7051,21 +7063,21 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7088,13 +7100,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7145,7 +7157,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7160,7 +7172,7 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
@@ -7171,10 +7183,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7197,13 +7209,13 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7230,31 +7242,31 @@
         <v>76</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7269,21 +7281,21 @@
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7306,13 +7318,13 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7363,7 +7375,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7378,21 +7390,21 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7415,13 +7427,13 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7472,7 +7484,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7487,21 +7499,21 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7524,13 +7536,13 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7557,13 +7569,13 @@
         <v>76</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>76</v>
@@ -7581,7 +7593,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7596,21 +7608,21 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7633,19 +7645,19 @@
         <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -7670,13 +7682,13 @@
         <v>76</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>76</v>
@@ -7694,7 +7706,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7715,15 +7727,15 @@
         <v>76</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7746,13 +7758,13 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7803,7 +7815,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -7818,13 +7830,13 @@
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
